--- a/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
+++ b/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
@@ -343,7 +343,19 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="11" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="8.25"/>
+    <col customWidth="1" min="6" max="7" width="11.63"/>
+    <col customWidth="1" min="8" max="8" width="10.13"/>
+    <col customWidth="1" min="9" max="9" width="12.38"/>
+    <col customWidth="1" min="10" max="10" width="10.13"/>
+    <col customWidth="1" min="11" max="11" width="5.25"/>
+    <col customWidth="1" min="12" max="12" width="8.5"/>
+    <col customWidth="1" min="13" max="13" width="7.25"/>
+    <col customWidth="1" min="14" max="26" width="12.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6566,7 +6578,19 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="11" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="9.38"/>
+    <col customWidth="1" min="6" max="7" width="11.63"/>
+    <col customWidth="1" min="8" max="8" width="10.13"/>
+    <col customWidth="1" min="9" max="9" width="12.38"/>
+    <col customWidth="1" min="10" max="10" width="10.13"/>
+    <col customWidth="1" min="11" max="11" width="5.25"/>
+    <col customWidth="1" min="12" max="12" width="8.5"/>
+    <col customWidth="1" min="13" max="13" width="7.25"/>
+    <col customWidth="1" min="14" max="24" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
+++ b/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
@@ -28596,15 +28596,15 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>0</v>
       </c>
       <c r="K2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>-1</v>
       </c>
       <c r="L2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>1</v>
       </c>
       <c r="M2" s="6">
@@ -41417,15 +41417,15 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>100000000</v>
       </c>
       <c r="K2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>99999999</v>
       </c>
       <c r="L2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>100000001</v>
       </c>
       <c r="M2" s="6">

--- a/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
+++ b/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>식별자 범위</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>액티브 스킬 샘플</t>
+  </si>
+  <si>
+    <t>패시브 스킬 샘플</t>
   </si>
 </sst>
 </file>
@@ -28614,7 +28617,7 @@
         <v>-1.0</v>
       </c>
       <c r="O2" s="7">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P2" s="7">
         <v>0.0</v>
@@ -41394,7 +41397,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="12">
         <v>1.0</v>
@@ -41435,7 +41438,7 @@
         <v>-1.0</v>
       </c>
       <c r="O2" s="7">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P2" s="7">
         <v>0.0</v>

--- a/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
+++ b/Templates/Tables/SkillInfo/SkillInfoTable.xlsx
@@ -28617,7 +28617,7 @@
         <v>-1.0</v>
       </c>
       <c r="O2" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P2" s="7">
         <v>0.0</v>
@@ -41438,7 +41438,7 @@
         <v>-1.0</v>
       </c>
       <c r="O2" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P2" s="7">
         <v>0.0</v>
